--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1698740977945</v>
+        <v>5.065104540891607</v>
       </c>
       <c r="D2" t="n">
-        <v>30.27352898896845</v>
+        <v>4.919448460707374</v>
       </c>
       <c r="E2" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F2" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.7500563395431</v>
+        <v>4.184384155175754</v>
       </c>
       <c r="D3" t="n">
-        <v>22.49234330792448</v>
+        <v>3.655005787537728</v>
       </c>
       <c r="E3" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F3" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.93961807110874</v>
+        <v>1.777687936555171</v>
       </c>
       <c r="D4" t="n">
-        <v>32.78124906500004</v>
+        <v>5.326952973062506</v>
       </c>
       <c r="E4" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F4" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.05177161180638</v>
+        <v>2.608412886918538</v>
       </c>
       <c r="D5" t="n">
-        <v>40.3386414231198</v>
+        <v>6.555029231256967</v>
       </c>
       <c r="E5" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F5" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.30211182974928</v>
+        <v>4.924093172334259</v>
       </c>
       <c r="D6" t="n">
-        <v>13.40825088022005</v>
+        <v>2.178840768035758</v>
       </c>
       <c r="E6" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F6" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.50211785862427</v>
+        <v>6.094094152026445</v>
       </c>
       <c r="D7" t="n">
-        <v>39.31645970746541</v>
+        <v>6.388924702463129</v>
       </c>
       <c r="E7" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F7" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.27594573411661</v>
+        <v>5.407341181793949</v>
       </c>
       <c r="D8" t="n">
-        <v>29.60574268617492</v>
+        <v>4.810933186503425</v>
       </c>
       <c r="E8" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F8" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.24214554143179</v>
+        <v>6.539348650482666</v>
       </c>
       <c r="D9" t="n">
-        <v>46.95210325427392</v>
+        <v>7.629716778819512</v>
       </c>
       <c r="E9" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F9" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.8998526098106</v>
+        <v>3.883726049094223</v>
       </c>
       <c r="D10" t="n">
-        <v>24.94528601423005</v>
+        <v>4.053608977312384</v>
       </c>
       <c r="E10" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F10" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.4705543931269</v>
+        <v>2.351465088883121</v>
       </c>
       <c r="D11" t="n">
-        <v>21.48449673743759</v>
+        <v>3.491230719833609</v>
       </c>
       <c r="E11" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F11" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.84011788719456</v>
+        <v>3.224019156669115</v>
       </c>
       <c r="D12" t="n">
-        <v>21.57252241898838</v>
+        <v>3.505534893085613</v>
       </c>
       <c r="E12" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F12" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.02925510499884</v>
+        <v>4.067253954562312</v>
       </c>
       <c r="D13" t="n">
-        <v>24.66948722736178</v>
+        <v>4.00879167444629</v>
       </c>
       <c r="E13" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F13" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.45300806392158</v>
+        <v>2.673613810387257</v>
       </c>
       <c r="D14" t="n">
-        <v>17.21469196191451</v>
+        <v>2.797387443811107</v>
       </c>
       <c r="E14" t="n">
-        <v>8.829060951106355</v>
+        <v>1.434722404554783</v>
       </c>
       <c r="F14" t="n">
-        <v>9.338805675678168</v>
+        <v>1.517555922297702</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
